--- a/docs/PRAP_Development_Plan_v2.39.xlsx
+++ b/docs/PRAP_Development_Plan_v2.39.xlsx
@@ -12254,17 +12254,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>PeriodWeightStandard</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>Default weight per project category x period. Seeds ProjectPeriod.</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>THE STANDARD MONTHLY FTE per project type, phase, work scope and period - where every figure gets its size (REQ-CAL-19).</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
